--- a/basedatos_partidas/salida/descompuestos/CT-08-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-02-040.xlsx
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.48</v>
+        <v>0.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.36</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>0.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.9</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="15">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>10.55</v>
+        <v>9.58</v>
       </c>
       <c r="H24" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>10.66</v>
+        <v>9.68</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-02-040.xlsx
@@ -617,10 +617,10 @@
         <v>0.14</v>
       </c>
       <c r="G13" t="n">
-        <v>8.5</v>
+        <v>32</v>
       </c>
       <c r="H13" t="n">
-        <v>1.19</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.93</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>9.58</v>
+        <v>12.87</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>9.68</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-02-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos cerámicos y porcelanato</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-02-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-02-040.xlsx
@@ -732,7 +732,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MO-OF1-SOL</t>
+          <t>MO-OF1-PISO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª solador.</t>
+          <t>Oficial de 1ª colocador de pisos.</t>
         </is>
       </c>
       <c r="F20" t="n">
